--- a/docs/FunCollection/FunCollection_5.xlsx
+++ b/docs/FunCollection/FunCollection_5.xlsx
@@ -552,63 +552,15 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF808080"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5A6BD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7F7F7F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46BDC6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="41">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -616,734 +568,45 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1642,79 +905,79 @@
     <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="39" t="s">
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="25" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1724,14 +987,14 @@
       <c r="D5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
@@ -1741,14 +1004,14 @@
       <c r="D6" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
@@ -1758,14 +1021,14 @@
       <c r="D7" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
@@ -1775,14 +1038,14 @@
       <c r="D8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>35</v>
       </c>
@@ -1792,14 +1055,14 @@
       <c r="D9" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>37</v>
       </c>
@@ -1809,14 +1072,14 @@
       <c r="D10" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="29" t="s">
+      <c r="F10" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
@@ -1826,14 +1089,14 @@
       <c r="D11" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>41</v>
       </c>
@@ -1843,953 +1106,952 @@
       <c r="D12" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="17" t="s">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="36" t="s">
+      <c r="G14" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="12" t="s">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="7" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="10" t="s">
+      <c r="B18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="H18" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="I18" s="18" t="s">
+      <c r="G18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
-      <c r="B19" s="44" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="23" t="s">
+      <c r="G19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="21" t="s">
+      <c r="I19" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="45"/>
-      <c r="B20" s="12" t="s">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F20" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H20" s="38" t="s">
+      <c r="H20" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I20" s="46"/>
-    </row>
-    <row r="21" spans="1:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I20" s="4"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="B24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K24" s="81" t="s">
+      <c r="I24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K24" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L24" s="82"/>
-      <c r="M24" s="82"/>
-      <c r="N24" s="82"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="47" t="s">
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="48"/>
-      <c r="B25" s="4" t="s">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G25" s="49" t="s">
+      <c r="G25" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J25" s="49" t="s">
+      <c r="J25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K25" s="84" t="s">
+      <c r="K25" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="86"/>
-      <c r="Q25" s="11" t="s">
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="51" t="s">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="51" t="s">
+      <c r="D26" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="52" t="s">
+      <c r="F26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G26" s="52"/>
-      <c r="H26" s="53">
+      <c r="G26" s="4"/>
+      <c r="H26" s="10">
         <v>40</v>
       </c>
-      <c r="I26" s="51" t="s">
+      <c r="I26" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J26" s="54" t="s">
+      <c r="J26" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="K26" s="52" t="s">
+      <c r="K26" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="L26" s="52" t="s">
+      <c r="L26" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M26" s="52"/>
-      <c r="N26" s="52"/>
-      <c r="O26" s="52"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="55"/>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="K30" s="47" t="s">
+      <c r="I30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="L30"/>
-      <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30"/>
-      <c r="P30"/>
-    </row>
-    <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48"/>
-      <c r="B31" s="4" t="s">
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="49" t="s">
+      <c r="D31" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J31" s="49" t="s">
+      <c r="J31" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="K31" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L31"/>
-      <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31"/>
-      <c r="P31"/>
-    </row>
-    <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="56"/>
-      <c r="B32" s="12" t="s">
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="12" t="s">
+      <c r="H32" s="4"/>
+      <c r="I32" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="K32" s="14"/>
-      <c r="L32"/>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-      <c r="P32"/>
-    </row>
-    <row r="35" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K32" s="4"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="57" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" s="43" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="G36" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="H36" s="43" t="s">
+      <c r="F36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="43" t="s">
+      <c r="I36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J36" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="K36" s="43" t="s">
+      <c r="J36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="58"/>
-      <c r="B37" s="4" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J37" s="4" t="s">
+      <c r="J37" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K37" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="51" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="51" t="s">
+      <c r="C38" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="59" t="s">
+      <c r="D38" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E38" s="60" t="s">
+      <c r="E38" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F38" s="61" t="s">
+      <c r="F38" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="13">
         <v>4</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="13">
         <v>3</v>
       </c>
-      <c r="J38" s="46"/>
-      <c r="K38" s="46"/>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="12" t="s">
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D39" s="59" t="s">
+      <c r="D39" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E39" s="32" t="s">
+      <c r="E39" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="13">
         <v>3</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="13">
         <v>2</v>
       </c>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46"/>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B42" s="2" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="62" t="s">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" s="63" t="s">
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="H43" s="64" t="s">
+      <c r="E43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="65"/>
-      <c r="B44" s="23" t="s">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="66" t="s">
+      <c r="D44" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E44" s="67" t="s">
+      <c r="E44" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F44" s="67" t="s">
+      <c r="F44" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G44" s="68" t="s">
+      <c r="G44" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H44" s="68" t="s">
+      <c r="H44" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="28"/>
-      <c r="B45" s="7" t="s">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="4"/>
+      <c r="B45" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E45" s="46" t="s">
+      <c r="E45" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F45" s="46" t="s">
+      <c r="F45" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G45" s="46" t="s">
+      <c r="G45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="H45" s="46"/>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H45" s="4"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="49" spans="1:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="62" t="s">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="G49" s="63" t="s">
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="I49" s="63" t="s">
+      <c r="H49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="K49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="L49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="M49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="N49" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="O49" s="64" t="s">
+      <c r="J49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="O49" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="65"/>
-      <c r="B50" s="23" t="s">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E50" s="67" t="s">
+      <c r="E50" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="67" t="s">
+      <c r="F50" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G50" s="67" t="s">
+      <c r="G50" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H50" s="67" t="s">
+      <c r="H50" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I50" s="67" t="s">
+      <c r="I50" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J50" s="67" t="s">
+      <c r="J50" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K50" s="67" t="s">
+      <c r="K50" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L50" s="67" t="s">
+      <c r="L50" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="M50" s="67" t="s">
+      <c r="M50" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="N50" s="67" t="s">
+      <c r="N50" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="O50" s="68" t="s">
+      <c r="O50" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="28"/>
-      <c r="B51" s="7" t="s">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E51" s="46" t="s">
+      <c r="E51" s="4" t="s">
         <v>75</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G51" s="69">
+      <c r="G51" s="13">
         <v>3</v>
       </c>
-      <c r="H51" s="46" t="s">
+      <c r="H51" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="I51" s="46" t="s">
+      <c r="I51" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="J51" s="46" t="s">
+      <c r="J51" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K51" s="46" t="s">
+      <c r="K51" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L51" s="46" t="s">
+      <c r="L51" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="M51" s="70" t="s">
+      <c r="M51" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="N51" s="46" t="s">
+      <c r="N51" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="O51" s="46"/>
-    </row>
-    <row r="54" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O51" s="4"/>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="1:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="62" t="s">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B55" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="D55" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="63" t="s">
+      <c r="B55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H55" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="I55" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="J55" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="K55" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="L55" s="64" t="s">
+      <c r="H55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="65"/>
-      <c r="B56" s="23" t="s">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="4"/>
+      <c r="B56" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E56" s="67" t="s">
+      <c r="E56" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F56" s="67" t="s">
+      <c r="F56" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G56" s="67" t="s">
+      <c r="G56" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="H56" s="67" t="s">
+      <c r="H56" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="I56" s="67" t="s">
+      <c r="I56" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J56" s="67" t="s">
+      <c r="J56" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K56" s="68" t="s">
+      <c r="K56" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L56" s="68" t="s">
+      <c r="L56" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="28"/>
-      <c r="B57" s="7" t="s">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="4"/>
+      <c r="B57" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="3" t="s">
         <v>143</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E57" s="46" t="s">
+      <c r="E57" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F57" s="46" t="s">
+      <c r="F57" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G57" s="72" t="s">
+      <c r="G57" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="H57" s="46" t="s">
+      <c r="H57" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I57" s="46" t="s">
+      <c r="I57" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="J57" s="46" t="s">
+      <c r="J57" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K57" s="71" t="s">
+      <c r="K57" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="L57" s="46"/>
-    </row>
-    <row r="60" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L57" s="4"/>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="61" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="73" t="s">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="D61" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="41" t="s">
+      <c r="B61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H61" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="I61" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="J61" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="K61" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="L61" s="42" t="s">
-        <v>6</v>
-      </c>
-      <c r="M61" s="42" t="s">
+      <c r="H61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M61" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N61" s="87" t="s">
+      <c r="N61" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="O61" s="87"/>
-      <c r="P61" s="76"/>
-      <c r="Q61" s="76"/>
-      <c r="R61" s="76"/>
-      <c r="S61" s="76"/>
-      <c r="T61" s="76"/>
-      <c r="U61" s="76"/>
-      <c r="V61" s="77"/>
-    </row>
-    <row r="62" spans="1:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="74"/>
-      <c r="B62" s="23" t="s">
+      <c r="O61" s="14"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A62" s="4"/>
+      <c r="B62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E62" s="67" t="s">
+      <c r="E62" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F62" s="67" t="s">
+      <c r="F62" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G62" s="67" t="s">
+      <c r="G62" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="H62" s="67" t="s">
+      <c r="H62" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I62" s="67" t="s">
+      <c r="I62" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J62" s="67" t="s">
+      <c r="J62" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K62" s="67" t="s">
+      <c r="K62" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="L62" s="67" t="s">
+      <c r="L62" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="M62" s="67" t="s">
+      <c r="M62" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N62" s="1" t="s">
@@ -2798,63 +2060,63 @@
       <c r="O62" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="P62" s="78"/>
-      <c r="Q62" s="78"/>
-      <c r="R62" s="78"/>
-      <c r="S62" s="78"/>
-      <c r="T62" s="78"/>
-      <c r="U62" s="78"/>
-      <c r="V62" s="79"/>
-    </row>
-    <row r="63" spans="1:22" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="75"/>
-      <c r="B63" s="7" t="s">
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A63" s="4"/>
+      <c r="B63" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="3" t="s">
         <v>146</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E63" s="46" t="s">
+      <c r="E63" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F63" s="46" t="s">
+      <c r="F63" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G63" s="46" t="s">
+      <c r="G63" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="H63" s="46" t="s">
+      <c r="H63" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="I63" s="46" t="s">
+      <c r="I63" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="J63" s="46" t="s">
+      <c r="J63" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="K63" s="46" t="s">
+      <c r="K63" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L63" s="58" t="s">
+      <c r="L63" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="M63" s="58"/>
-      <c r="N63" s="80" t="s">
+      <c r="M63" s="4"/>
+      <c r="N63" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="O63" s="80" t="s">
+      <c r="O63" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
+      <c r="P63" s="3"/>
+      <c r="Q63" s="3"/>
+      <c r="R63" s="3"/>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="3"/>
+      <c r="V63" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
